--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119791346</v>
       </c>
       <c r="B2" t="n">
-        <v>84009</v>
+        <v>84026</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,219 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122645617</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91792</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lilliden, Stora blåsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>459894</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7187675</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122645511</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99495</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lilliden, Stora blåsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>459855</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7187688</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645617</v>
+        <v>122645511</v>
       </c>
       <c r="B3" t="n">
-        <v>91792</v>
+        <v>99495</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,26 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4787</v>
+        <v>2082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459894</v>
+        <v>459855</v>
       </c>
       <c r="R3" t="n">
-        <v>7187675</v>
+        <v>7187688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645511</v>
+        <v>122645617</v>
       </c>
       <c r="B4" t="n">
-        <v>99495</v>
+        <v>91792</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,27 +900,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2082</v>
+        <v>4787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459855</v>
+        <v>459894</v>
       </c>
       <c r="R4" t="n">
-        <v>7187688</v>
+        <v>7187675</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645511</v>
+        <v>122645617</v>
       </c>
       <c r="B3" t="n">
-        <v>99495</v>
+        <v>91793</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,27 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2082</v>
+        <v>4787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -821,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459855</v>
+        <v>459894</v>
       </c>
       <c r="R3" t="n">
-        <v>7187688</v>
+        <v>7187675</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645617</v>
+        <v>122645511</v>
       </c>
       <c r="B4" t="n">
-        <v>91792</v>
+        <v>99496</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,26 +899,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4787</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459894</v>
+        <v>459855</v>
       </c>
       <c r="R4" t="n">
-        <v>7187675</v>
+        <v>7187688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>122645617</v>
       </c>
       <c r="B3" t="n">
-        <v>91793</v>
+        <v>91796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>122645511</v>
       </c>
       <c r="B4" t="n">
-        <v>99496</v>
+        <v>99499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645617</v>
+        <v>122645511</v>
       </c>
       <c r="B3" t="n">
-        <v>91796</v>
+        <v>99499</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,26 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4787</v>
+        <v>2082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459894</v>
+        <v>459855</v>
       </c>
       <c r="R3" t="n">
-        <v>7187675</v>
+        <v>7187688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645511</v>
+        <v>122645617</v>
       </c>
       <c r="B4" t="n">
-        <v>99499</v>
+        <v>91796</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,27 +900,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2082</v>
+        <v>4787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459855</v>
+        <v>459894</v>
       </c>
       <c r="R4" t="n">
-        <v>7187688</v>
+        <v>7187675</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645511</v>
+        <v>122645617</v>
       </c>
       <c r="B3" t="n">
-        <v>99602</v>
+        <v>91899</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,27 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2082</v>
+        <v>4787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -821,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459855</v>
+        <v>459894</v>
       </c>
       <c r="R3" t="n">
-        <v>7187688</v>
+        <v>7187675</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645617</v>
+        <v>122645511</v>
       </c>
       <c r="B4" t="n">
-        <v>91899</v>
+        <v>99602</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,26 +899,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4787</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459894</v>
+        <v>459855</v>
       </c>
       <c r="R4" t="n">
-        <v>7187675</v>
+        <v>7187688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>122645617</v>
       </c>
       <c r="B3" t="n">
-        <v>91899</v>
+        <v>91903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>122645511</v>
       </c>
       <c r="B4" t="n">
-        <v>99602</v>
+        <v>99610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645617</v>
+        <v>122645511</v>
       </c>
       <c r="B3" t="n">
-        <v>91903</v>
+        <v>99610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,26 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4787</v>
+        <v>2082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459894</v>
+        <v>459855</v>
       </c>
       <c r="R3" t="n">
-        <v>7187675</v>
+        <v>7187688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645511</v>
+        <v>122645617</v>
       </c>
       <c r="B4" t="n">
-        <v>99610</v>
+        <v>91903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,27 +900,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2082</v>
+        <v>4787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459855</v>
+        <v>459894</v>
       </c>
       <c r="R4" t="n">
-        <v>7187688</v>
+        <v>7187675</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645511</v>
+        <v>122645617</v>
       </c>
       <c r="B3" t="n">
-        <v>99610</v>
+        <v>91903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,27 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2082</v>
+        <v>4787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -821,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459855</v>
+        <v>459894</v>
       </c>
       <c r="R3" t="n">
-        <v>7187688</v>
+        <v>7187675</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645617</v>
+        <v>122645511</v>
       </c>
       <c r="B4" t="n">
-        <v>91903</v>
+        <v>99612</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,26 +899,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4787</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459894</v>
+        <v>459855</v>
       </c>
       <c r="R4" t="n">
-        <v>7187675</v>
+        <v>7187688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63243-2023 artfynd.xlsx
+++ b/artfynd/A 63243-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>122645617</v>
       </c>
       <c r="B3" t="n">
-        <v>91903</v>
+        <v>91911</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>122645511</v>
       </c>
       <c r="B4" t="n">
-        <v>99612</v>
+        <v>99620</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
